--- a/Forecasts/Forecast-25062026-0Z.xlsx
+++ b/Forecasts/Forecast-25062026-0Z.xlsx
@@ -620,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -640,6 +640,7 @@
     <col width="11" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -652,7 +653,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Généré le : 25/06/2026 11:36</t>
+          <t>Généré le : 26/06/2026 09:46</t>
         </is>
       </c>
     </row>
@@ -736,15 +737,20 @@
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
+          <t>GEFS DET</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
           <t>GEFS P90</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>GEFS Spread</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>Divergence Modèles</t>
         </is>
@@ -796,12 +802,15 @@
         <v>21.9</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q6" s="9" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="Q6" s="8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R6" s="9" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -851,12 +860,15 @@
         <v>20.8</v>
       </c>
       <c r="O7" s="8" t="n">
-        <v>21.7</v>
+        <v>20.3</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q7" s="9" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="Q7" s="8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R7" s="9" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -906,12 +918,15 @@
         <v>21.6</v>
       </c>
       <c r="O8" s="8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="P8" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="P8" s="8" t="n">
+      <c r="Q8" s="8" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q8" s="9" t="n">
+      <c r="R8" s="9" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -961,12 +976,15 @@
         <v>14.9</v>
       </c>
       <c r="O9" s="8" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="P9" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="P9" s="8" t="n">
+      <c r="Q9" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="Q9" s="8" t="n">
+      <c r="R9" s="8" t="n">
         <v>1.6</v>
       </c>
     </row>
@@ -1013,16 +1031,19 @@
         <v>9.5</v>
       </c>
       <c r="N10" s="8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="O10" s="8" t="n">
         <v>11.6</v>
       </c>
-      <c r="O10" s="8" t="n">
+      <c r="P10" s="8" t="n">
         <v>13.2</v>
       </c>
-      <c r="P10" s="8" t="n">
+      <c r="Q10" s="8" t="n">
         <v>3.7</v>
       </c>
-      <c r="Q10" s="8" t="n">
-        <v>3.3</v>
+      <c r="R10" s="8" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="11">
@@ -1068,16 +1089,19 @@
         <v>8.5</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>15.8</v>
+        <v>10.3</v>
       </c>
       <c r="P11" s="8" t="n">
-        <v>7.3</v>
+        <v>15.9</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>2.8</v>
+        <v>7.4</v>
+      </c>
+      <c r="R11" s="8" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="12">
@@ -1126,12 +1150,15 @@
         <v>11.4</v>
       </c>
       <c r="O12" s="8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="P12" s="8" t="n">
         <v>14.9</v>
       </c>
-      <c r="P12" s="8" t="n">
+      <c r="Q12" s="8" t="n">
         <v>5.6</v>
       </c>
-      <c r="Q12" s="8" t="n">
+      <c r="R12" s="8" t="n">
         <v>3.1</v>
       </c>
     </row>
@@ -1178,16 +1205,19 @@
         <v>8.1</v>
       </c>
       <c r="N13" s="8" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="O13" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="P13" s="8" t="n">
         <v>15.2</v>
       </c>
-      <c r="P13" s="8" t="n">
+      <c r="Q13" s="8" t="n">
         <v>7.1</v>
       </c>
-      <c r="Q13" s="8" t="n">
-        <v>2.4</v>
+      <c r="R13" s="8" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
@@ -1233,16 +1263,19 @@
         <v>7.2</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>11.6</v>
+        <v>12.2</v>
       </c>
       <c r="O14" s="8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="P14" s="8" t="n">
         <v>16.3</v>
       </c>
-      <c r="P14" s="8" t="n">
+      <c r="Q14" s="8" t="n">
         <v>9.1</v>
       </c>
-      <c r="Q14" s="8" t="n">
-        <v>2.8</v>
+      <c r="R14" s="8" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="15">
@@ -1285,18 +1318,21 @@
         <v>6.2</v>
       </c>
       <c r="M15" s="8" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="N15" s="8" t="n">
         <v>11.8</v>
       </c>
       <c r="O15" s="8" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="P15" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="P15" s="8" t="n">
-        <v>9.6</v>
-      </c>
       <c r="Q15" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="R15" s="8" t="n">
         <v>3.7</v>
       </c>
     </row>
@@ -1340,19 +1376,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="M16" s="8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="N16" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="O16" s="8" t="n">
         <v>7.6</v>
       </c>
-      <c r="N16" s="8" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="O16" s="8" t="n">
-        <v>16.7</v>
-      </c>
       <c r="P16" s="8" t="n">
-        <v>9.1</v>
+        <v>16.8</v>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>3.4</v>
+        <v>9</v>
+      </c>
+      <c r="R16" s="8" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="17">
@@ -1395,19 +1434,22 @@
         <v>9.4</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="N17" s="8" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="O17" s="8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="P17" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="P17" s="8" t="n">
-        <v>11.1</v>
-      </c>
       <c r="Q17" s="8" t="n">
-        <v>2.2</v>
+        <v>11.3</v>
+      </c>
+      <c r="R17" s="8" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="18">
@@ -1453,16 +1495,19 @@
         <v>6.4</v>
       </c>
       <c r="N18" s="8" t="n">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="O18" s="8" t="n">
-        <v>17.3</v>
+        <v>7.6</v>
       </c>
       <c r="P18" s="8" t="n">
-        <v>10.9</v>
+        <v>17.4</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>2.6</v>
+        <v>11</v>
+      </c>
+      <c r="R18" s="8" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="19">
@@ -1505,19 +1550,22 @@
         <v>10.8</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="N19" s="8" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="O19" s="8" t="n">
-        <v>18.2</v>
+        <v>5.9</v>
       </c>
       <c r="P19" s="8" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="Q19" s="8" t="n">
         <v>12.2</v>
       </c>
-      <c r="Q19" s="10" t="n">
-        <v>4</v>
+      <c r="R19" s="10" t="n">
+        <v>4.1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1608,22 @@
         <v>12.1</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="N20" s="8" t="n">
-        <v>13.6</v>
+        <v>13.9</v>
       </c>
       <c r="O20" s="8" t="n">
-        <v>19.7</v>
+        <v>5.7</v>
       </c>
       <c r="P20" s="8" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="Q20" s="10" t="n">
-        <v>4.5</v>
+        <v>19.8</v>
+      </c>
+      <c r="Q20" s="8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="R20" s="10" t="n">
+        <v>4.8</v>
       </c>
     </row>
     <row r="21">
@@ -1618,15 +1669,18 @@
         <v>7.6</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="O21" s="8" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="P21" s="8" t="n">
         <v>15.7</v>
       </c>
-      <c r="P21" s="8" t="n">
+      <c r="Q21" s="8" t="n">
         <v>8.1</v>
       </c>
-      <c r="Q21" s="9" t="n">
+      <c r="R21" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1641,7 +1695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1663,6 +1717,7 @@
     <col width="11" customWidth="1" min="17" max="17"/>
     <col width="11" customWidth="1" min="18" max="18"/>
     <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1675,7 +1730,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Généré le : 25/06/2026 11:36</t>
+          <t>Généré le : 26/06/2026 09:46</t>
         </is>
       </c>
     </row>
@@ -1727,57 +1782,62 @@
           <t>AIFS DET</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>GEFS DET</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>P75</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>P90</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>Spread</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>Ecart-type</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>Proba &gt; 20°</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>Δ 24-Jun 12Z</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>Δ 24-Jun 0Z</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>Δ 23-Jun 12Z</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>Δ 23-Jun 0Z</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>Δ 22-Jun 12Z</t>
         </is>
@@ -1811,36 +1871,39 @@
         <v>21.5</v>
       </c>
       <c r="I6" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="J6" s="8" t="n">
         <v>21.8</v>
       </c>
-      <c r="J6" s="8" t="n">
+      <c r="K6" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="K6" s="8" t="n">
+      <c r="L6" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="L6" s="8" t="n">
+      <c r="M6" s="8" t="n">
         <v>1.1</v>
       </c>
-      <c r="M6" s="8" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="N6" s="11" t="n">
+      <c r="N6" s="8" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="O6" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="O6" s="8" t="n">
+      <c r="P6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="10" t="n">
+      <c r="Q6" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="9" t="n">
+      <c r="R6" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="R6" s="10" t="n">
+      <c r="S6" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="S6" s="10" t="n">
+      <c r="T6" s="10" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -1872,36 +1935,39 @@
         <v>20.9</v>
       </c>
       <c r="I7" s="8" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="J7" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="J7" s="8" t="n">
+      <c r="K7" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="K7" s="8" t="n">
+      <c r="L7" s="8" t="n">
         <v>22.3</v>
       </c>
-      <c r="L7" s="8" t="n">
+      <c r="M7" s="8" t="n">
         <v>1.6</v>
       </c>
-      <c r="M7" s="8" t="n">
+      <c r="N7" s="8" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="N7" s="11" t="n">
-        <v>0.7293233082706767</v>
-      </c>
-      <c r="O7" s="9" t="n">
-        <v>-0.2</v>
+      <c r="O7" s="11" t="n">
+        <v>0.7272727272727273</v>
       </c>
       <c r="P7" s="9" t="n">
         <v>-0.2</v>
       </c>
       <c r="Q7" s="9" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="R7" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="R7" s="10" t="n">
+      <c r="S7" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="S7" s="9" t="n">
+      <c r="T7" s="9" t="n">
         <v>-0.7</v>
       </c>
     </row>
@@ -1933,36 +1999,39 @@
         <v>20.1</v>
       </c>
       <c r="I8" s="8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="J8" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="J8" s="8" t="n">
+      <c r="K8" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="K8" s="8" t="n">
+      <c r="L8" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="L8" s="8" t="n">
+      <c r="M8" s="8" t="n">
         <v>3.3</v>
       </c>
-      <c r="M8" s="8" t="n">
+      <c r="N8" s="8" t="n">
         <v>1.32</v>
       </c>
-      <c r="N8" s="11" t="n">
-        <v>0.7969924812030075</v>
-      </c>
-      <c r="O8" s="9" t="n">
+      <c r="O8" s="11" t="n">
+        <v>0.7954545454545454</v>
+      </c>
+      <c r="P8" s="9" t="n">
         <v>-0.4</v>
       </c>
-      <c r="P8" s="10" t="n">
+      <c r="Q8" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q8" s="10" t="n">
+      <c r="R8" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="R8" s="10" t="n">
+      <c r="S8" s="10" t="n">
         <v>1.3</v>
       </c>
-      <c r="S8" s="10" t="n">
+      <c r="T8" s="10" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1994,36 +2063,39 @@
         <v>12.5</v>
       </c>
       <c r="I9" s="8" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J9" s="8" t="n">
         <v>15.2</v>
       </c>
-      <c r="J9" s="8" t="n">
+      <c r="K9" s="8" t="n">
         <v>16.7</v>
       </c>
-      <c r="K9" s="8" t="n">
+      <c r="L9" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="L9" s="8" t="n">
+      <c r="M9" s="8" t="n">
         <v>5.1</v>
       </c>
-      <c r="M9" s="8" t="n">
+      <c r="N9" s="8" t="n">
         <v>1.96</v>
       </c>
-      <c r="N9" s="11" t="n">
-        <v>0.007518796992481203</v>
-      </c>
-      <c r="O9" s="9" t="n">
+      <c r="O9" s="11" t="n">
+        <v>0.007575757575757576</v>
+      </c>
+      <c r="P9" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="P9" s="9" t="n">
+      <c r="Q9" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="Q9" s="9" t="n">
+      <c r="R9" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="R9" s="9" t="n">
+      <c r="S9" s="9" t="n">
         <v>-2.2</v>
       </c>
-      <c r="S9" s="9" t="n">
+      <c r="T9" s="9" t="n">
         <v>-2.6</v>
       </c>
     </row>
@@ -2055,36 +2127,39 @@
         <v>8.5</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>10.8</v>
+        <v>11.6</v>
       </c>
       <c r="J10" s="8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="K10" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="K10" s="8" t="n">
+      <c r="L10" s="8" t="n">
         <v>17.3</v>
       </c>
-      <c r="L10" s="8" t="n">
+      <c r="M10" s="8" t="n">
         <v>5.2</v>
       </c>
-      <c r="M10" s="8" t="n">
+      <c r="N10" s="8" t="n">
         <v>2.17</v>
       </c>
-      <c r="N10" s="11" t="n">
+      <c r="O10" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="O10" s="9" t="n">
+      <c r="P10" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="P10" s="10" t="n">
+      <c r="Q10" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q10" s="9" t="n">
+      <c r="R10" s="9" t="n">
         <v>-1.2</v>
       </c>
-      <c r="R10" s="9" t="n">
+      <c r="S10" s="9" t="n">
         <v>-2.6</v>
       </c>
-      <c r="S10" s="9" t="n">
+      <c r="T10" s="9" t="n">
         <v>-3.5</v>
       </c>
     </row>
@@ -2116,36 +2191,39 @@
         <v>9.6</v>
       </c>
       <c r="I11" s="8" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J11" s="8" t="n">
         <v>10.9</v>
       </c>
-      <c r="J11" s="8" t="n">
+      <c r="K11" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="K11" s="8" t="n">
+      <c r="L11" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="L11" s="8" t="n">
+      <c r="M11" s="8" t="n">
         <v>6.2</v>
       </c>
-      <c r="M11" s="8" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="N11" s="11" t="n">
+      <c r="N11" s="8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="O11" s="9" t="n">
+      <c r="P11" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="P11" s="10" t="n">
+      <c r="Q11" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="R11" s="9" t="n">
         <v>-0.8</v>
       </c>
-      <c r="R11" s="9" t="n">
+      <c r="S11" s="9" t="n">
         <v>-2.1</v>
       </c>
-      <c r="S11" s="9" t="n">
+      <c r="T11" s="9" t="n">
         <v>-3.8</v>
       </c>
     </row>
@@ -2177,36 +2255,39 @@
         <v>8.699999999999999</v>
       </c>
       <c r="I12" s="8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J12" s="8" t="n">
         <v>10.3</v>
       </c>
-      <c r="J12" s="8" t="n">
+      <c r="K12" s="8" t="n">
         <v>12.6</v>
       </c>
-      <c r="K12" s="8" t="n">
+      <c r="L12" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="L12" s="8" t="n">
+      <c r="M12" s="8" t="n">
         <v>5.5</v>
       </c>
-      <c r="M12" s="8" t="n">
+      <c r="N12" s="8" t="n">
         <v>2.3</v>
       </c>
-      <c r="N12" s="11" t="n">
+      <c r="O12" s="11" t="n">
         <v>0</v>
-      </c>
-      <c r="O12" s="10" t="n">
-        <v>0.1</v>
       </c>
       <c r="P12" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q12" s="9" t="n">
+      <c r="Q12" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R12" s="9" t="n">
         <v>-0.5</v>
       </c>
-      <c r="R12" s="9" t="n">
+      <c r="S12" s="9" t="n">
         <v>-1.4</v>
       </c>
-      <c r="S12" s="9" t="n">
+      <c r="T12" s="9" t="n">
         <v>-2.8</v>
       </c>
     </row>
@@ -2238,36 +2319,39 @@
         <v>8.699999999999999</v>
       </c>
       <c r="I13" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="J13" s="8" t="n">
         <v>11.7</v>
       </c>
-      <c r="J13" s="8" t="n">
+      <c r="K13" s="8" t="n">
         <v>13.9</v>
       </c>
-      <c r="K13" s="8" t="n">
+      <c r="L13" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="L13" s="8" t="n">
+      <c r="M13" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="M13" s="8" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="N13" s="11" t="n">
+      <c r="N13" s="8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="10" t="n">
+      <c r="P13" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="P13" s="10" t="n">
+      <c r="Q13" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q13" s="10" t="n">
+      <c r="R13" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="R13" s="9" t="n">
+      <c r="S13" s="9" t="n">
         <v>-0.1</v>
       </c>
-      <c r="S13" s="9" t="n">
+      <c r="T13" s="9" t="n">
         <v>-1.5</v>
       </c>
     </row>
@@ -2299,36 +2383,39 @@
         <v>7.6</v>
       </c>
       <c r="I14" s="8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J14" s="8" t="n">
         <v>11.6</v>
       </c>
-      <c r="J14" s="8" t="n">
+      <c r="K14" s="8" t="n">
         <v>14.4</v>
       </c>
-      <c r="K14" s="8" t="n">
+      <c r="L14" s="8" t="n">
         <v>18.3</v>
       </c>
-      <c r="L14" s="8" t="n">
+      <c r="M14" s="8" t="n">
         <v>8.1</v>
       </c>
-      <c r="M14" s="8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N14" s="11" t="n">
+      <c r="N14" s="8" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="O14" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="9" t="n">
+      <c r="P14" s="9" t="n">
         <v>-0.2</v>
       </c>
-      <c r="P14" s="10" t="n">
+      <c r="Q14" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q14" s="10" t="n">
+      <c r="R14" s="10" t="n">
         <v>0.9</v>
       </c>
-      <c r="R14" s="9" t="n">
+      <c r="S14" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="S14" s="9" t="n">
+      <c r="T14" s="9" t="n">
         <v>-2.1</v>
       </c>
     </row>
@@ -2360,36 +2447,39 @@
         <v>8.4</v>
       </c>
       <c r="I15" s="8" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J15" s="8" t="n">
         <v>10.8</v>
       </c>
-      <c r="J15" s="8" t="n">
+      <c r="K15" s="8" t="n">
         <v>14.3</v>
       </c>
-      <c r="K15" s="8" t="n">
+      <c r="L15" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="L15" s="8" t="n">
+      <c r="M15" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="M15" s="8" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="N15" s="11" t="n">
-        <v>0.02255639097744361</v>
-      </c>
-      <c r="O15" s="9" t="n">
+      <c r="N15" s="8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O15" s="11" t="n">
+        <v>0.02272727272727273</v>
+      </c>
+      <c r="P15" s="9" t="n">
         <v>-0.7</v>
       </c>
-      <c r="P15" s="10" t="n">
+      <c r="Q15" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q15" s="10" t="n">
+      <c r="R15" s="10" t="n">
         <v>0.6</v>
       </c>
-      <c r="R15" s="9" t="n">
+      <c r="S15" s="9" t="n">
         <v>-1</v>
       </c>
-      <c r="S15" s="9" t="n">
+      <c r="T15" s="9" t="n">
         <v>-2.3</v>
       </c>
     </row>
@@ -2412,7 +2502,7 @@
         <v>6.2</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>8.199999999999999</v>
@@ -2421,37 +2511,40 @@
         <v>13.9</v>
       </c>
       <c r="I16" s="8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J16" s="8" t="n">
         <v>11.3</v>
       </c>
-      <c r="J16" s="8" t="n">
+      <c r="K16" s="8" t="n">
         <v>14.3</v>
       </c>
-      <c r="K16" s="8" t="n">
+      <c r="L16" s="8" t="n">
         <v>22.4</v>
       </c>
-      <c r="L16" s="8" t="n">
+      <c r="M16" s="8" t="n">
         <v>9.6</v>
       </c>
-      <c r="M16" s="8" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="N16" s="11" t="n">
-        <v>0.01503759398496241</v>
-      </c>
-      <c r="O16" s="10" t="n">
+      <c r="N16" s="8" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="O16" s="11" t="n">
+        <v>0.01515151515151515</v>
+      </c>
+      <c r="P16" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q16" s="10" t="n">
         <v>0.7</v>
       </c>
-      <c r="P16" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q16" s="10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="R16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="9" t="n">
-        <v>-1.1</v>
+      <c r="R16" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="S16" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T16" s="9" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="17">
@@ -2470,7 +2563,7 @@
         <v>5.1</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="F17" s="8" t="n">
         <v>9</v>
@@ -2482,36 +2575,39 @@
         <v>11.3</v>
       </c>
       <c r="I17" s="8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J17" s="8" t="n">
         <v>13.1</v>
       </c>
-      <c r="J17" s="8" t="n">
-        <v>15.2</v>
-      </c>
       <c r="K17" s="8" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="L17" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="L17" s="8" t="n">
-        <v>10.1</v>
-      </c>
       <c r="M17" s="8" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="N17" s="11" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="N17" s="8" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="O17" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="O17" s="10" t="n">
+      <c r="P17" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="P17" s="10" t="n">
+      <c r="Q17" s="10" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q17" s="10" t="n">
+      <c r="R17" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="R17" s="9" t="n">
+      <c r="S17" s="9" t="n">
         <v>-0.3</v>
       </c>
-      <c r="S17" s="9" t="n">
+      <c r="T17" s="9" t="n">
         <v>-1.5</v>
       </c>
     </row>
@@ -2528,7 +2624,7 @@
         <v>2.2</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="E18" s="8" t="n">
         <v>6.8</v>
@@ -2543,36 +2639,39 @@
         <v>13.2</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>13.4</v>
+        <v>7.6</v>
       </c>
       <c r="J18" s="8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="K18" s="8" t="n">
         <v>16.2</v>
       </c>
-      <c r="K18" s="8" t="n">
+      <c r="L18" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="L18" s="8" t="n">
-        <v>10.9</v>
-      </c>
       <c r="M18" s="8" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="N18" s="11" t="n">
-        <v>0.01503759398496241</v>
-      </c>
-      <c r="O18" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N18" s="8" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="O18" s="11" t="n">
+        <v>0.01515151515151515</v>
+      </c>
+      <c r="P18" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="P18" s="8" t="n">
+      <c r="Q18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" s="10" t="n">
+      <c r="R18" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="R18" s="9" t="n">
+      <c r="S18" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="S18" s="9" t="n">
+      <c r="T18" s="9" t="n">
         <v>-0.8</v>
       </c>
     </row>
@@ -2592,7 +2691,7 @@
         <v>5.3</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="F19" s="8" t="n">
         <v>9.4</v>
@@ -2604,36 +2703,39 @@
         <v>15.4</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>13.9</v>
+        <v>5.9</v>
       </c>
       <c r="J19" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="K19" s="8" t="n">
         <v>17.4</v>
       </c>
-      <c r="K19" s="8" t="n">
+      <c r="L19" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="L19" s="8" t="n">
+      <c r="M19" s="8" t="n">
         <v>12.1</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="N19" s="8" t="n">
         <v>4.5</v>
       </c>
-      <c r="N19" s="11" t="n">
-        <v>0.01503759398496241</v>
-      </c>
-      <c r="O19" s="8" t="n">
+      <c r="O19" s="11" t="n">
+        <v>0.01515151515151515</v>
+      </c>
+      <c r="P19" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="P19" s="9" t="n">
+      <c r="Q19" s="9" t="n">
         <v>-0.9</v>
       </c>
-      <c r="Q19" s="10" t="n">
+      <c r="R19" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="R19" s="9" t="n">
+      <c r="S19" s="9" t="n">
         <v>-1.1</v>
       </c>
-      <c r="S19" s="9" t="n">
+      <c r="T19" s="9" t="n">
         <v>-2.7</v>
       </c>
     </row>
@@ -2665,36 +2767,39 @@
         <v>17.6</v>
       </c>
       <c r="I20" s="8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J20" s="8" t="n">
         <v>14.9</v>
       </c>
-      <c r="J20" s="8" t="n">
-        <v>18.9</v>
-      </c>
       <c r="K20" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="L20" s="8" t="n">
         <v>22.2</v>
       </c>
-      <c r="L20" s="8" t="n">
-        <v>13.4</v>
-      </c>
       <c r="M20" s="8" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="N20" s="11" t="n">
-        <v>0.07518796992481203</v>
-      </c>
-      <c r="O20" s="10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="N20" s="8" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="O20" s="11" t="n">
+        <v>0.07575757575757576</v>
+      </c>
+      <c r="P20" s="10" t="n">
         <v>1.1</v>
       </c>
-      <c r="P20" s="9" t="n">
+      <c r="Q20" s="9" t="n">
         <v>-2.4</v>
       </c>
-      <c r="Q20" s="9" t="n">
+      <c r="R20" s="9" t="n">
         <v>-1.9</v>
       </c>
-      <c r="R20" s="8" t="n">
+      <c r="S20" s="8" t="n">
         <v/>
       </c>
-      <c r="S20" s="8" t="n">
+      <c r="T20" s="8" t="n">
         <v/>
       </c>
     </row>
@@ -2714,10 +2819,10 @@
         <v>7.6</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="G21" s="8" t="n">
         <v/>
@@ -2726,28 +2831,28 @@
         <v/>
       </c>
       <c r="I21" s="8" t="n">
-        <v>14.5</v>
+        <v>10.3</v>
       </c>
       <c r="J21" s="8" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="K21" s="8" t="n">
         <v>15.7</v>
       </c>
-      <c r="K21" s="8" t="n">
+      <c r="L21" s="8" t="n">
         <v>22.5</v>
       </c>
-      <c r="L21" s="8" t="n">
+      <c r="M21" s="8" t="n">
         <v>8.1</v>
       </c>
-      <c r="M21" s="8" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="N21" s="11" t="n">
-        <v>0.03125</v>
-      </c>
-      <c r="O21" s="10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P21" s="8" t="n">
-        <v/>
+      <c r="N21" s="8" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="O21" s="11" t="n">
+        <v>0.03225806451612903</v>
+      </c>
+      <c r="P21" s="10" t="n">
+        <v>1.8</v>
       </c>
       <c r="Q21" s="8" t="n">
         <v/>
@@ -2756,6 +2861,9 @@
         <v/>
       </c>
       <c r="S21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="T21" s="8" t="n">
         <v/>
       </c>
     </row>
